--- a/artfynd/A 29119-2026 artfynd.xlsx
+++ b/artfynd/A 29119-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AZ121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869443</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869445</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869446</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869447</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869449</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869450</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869451</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869800</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869801</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869802</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869804</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869805</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869806</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869808</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869809</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869811</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869812</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869813</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869814</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869599</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869600</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869601</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869602</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869603</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869533</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869534</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869840</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869553</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869474</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3978,6 +4148,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869653</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4075,6 +4250,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869655</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4172,6 +4352,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869657</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4269,6 +4454,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869658</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4366,6 +4556,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869660</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4463,6 +4658,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869661</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4560,6 +4760,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869663</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4657,6 +4862,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869664</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4754,6 +4964,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869665</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4851,6 +5066,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869666</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4948,6 +5168,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869667</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5045,6 +5270,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869669</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5142,6 +5372,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869670</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5239,6 +5474,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869671</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5336,6 +5576,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869672</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5433,6 +5678,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869673</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5530,6 +5780,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869676</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5627,6 +5882,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869678</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5724,6 +5984,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869679</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5821,6 +6086,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869680</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5918,6 +6188,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869681</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6015,6 +6290,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869682</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6112,6 +6392,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869683</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6209,6 +6494,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869684</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6306,6 +6596,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869685</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6403,6 +6698,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869687</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6500,6 +6800,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869688</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6597,6 +6902,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869689</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6694,6 +7004,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869691</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6791,6 +7106,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869692</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6888,6 +7208,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869693</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6985,6 +7310,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869694</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7082,6 +7412,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869695</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7179,6 +7514,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869697</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7276,6 +7616,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869698</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7373,6 +7718,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869699</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7470,6 +7820,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869700</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7567,6 +7922,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869701</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7664,6 +8024,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869702</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7761,6 +8126,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869703</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7858,6 +8228,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869705</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7955,6 +8330,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869706</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8052,6 +8432,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869707</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8149,6 +8534,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869708</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8246,6 +8636,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869709</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8343,6 +8738,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869710</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8440,6 +8840,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869711</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8537,6 +8942,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869712</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8634,6 +9044,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869714</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8731,6 +9146,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869715</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8828,6 +9248,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869716</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8925,6 +9350,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869717</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9022,6 +9452,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869719</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9119,6 +9554,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869720</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9216,6 +9656,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869721</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9313,6 +9758,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869722</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9410,6 +9860,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869723</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9507,6 +9962,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869724</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9604,6 +10064,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869725</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9701,6 +10166,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869726</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9798,6 +10268,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869727</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9895,6 +10370,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869642</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9992,6 +10472,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869440</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10089,6 +10574,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869609</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10186,6 +10676,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869610</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10283,6 +10778,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869611</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10380,6 +10880,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869477</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10477,6 +10982,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869479</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10574,6 +11084,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869482</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10671,6 +11186,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869483</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10768,6 +11288,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869484</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10865,6 +11390,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869485</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10962,6 +11492,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869486</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11059,6 +11594,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869487</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11156,6 +11696,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869488</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11253,6 +11798,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869489</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11350,6 +11900,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869490</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11447,6 +12002,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869491</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11552,6 +12112,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869567</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11657,6 +12222,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869539</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11762,6 +12332,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869867</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11867,6 +12442,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869544</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11972,6 +12552,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869545</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12079,6 +12664,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869551</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12184,6 +12774,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869643</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12281,6 +12876,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869649</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12391,8 +12991,135 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116869637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>